--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99306</v>
+        <v>99307</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106380</v>
+        <v>106381</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99307</v>
+        <v>99320</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106381</v>
+        <v>106394</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99320</v>
+        <v>99321</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106394</v>
+        <v>106395</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99321</v>
+        <v>99324</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106395</v>
+        <v>106398</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106398</v>
+        <v>106399</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ426"/>
+  <dimension ref="A1:AZ427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43366,50 +43366,59 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>73702559</v>
+        <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>92348</v>
+        <v>93404</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I383" t="inlineStr"/>
-      <c r="J383" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
         <is>
-          <t>Hemträsket, S om sydspetsen, Srm</t>
+          <t>Kärrgrav, Srm</t>
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>698490</v>
+        <v>698454</v>
       </c>
       <c r="R383" t="n">
-        <v>6555875</v>
+        <v>6556015</v>
       </c>
       <c r="S383" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -43433,12 +43442,22 @@
       </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -43447,31 +43466,30 @@
       <c r="AE383" t="b">
         <v>0</v>
       </c>
-      <c r="AF383" t="inlineStr"/>
       <c r="AG383" t="b">
         <v>0</v>
       </c>
       <c r="AT383" t="inlineStr"/>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702559</t>
+          <t>https://artportalen.se/Sighting/136730156</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>107498521</v>
+        <v>73702559</v>
       </c>
       <c r="B384" t="n">
         <v>92348</v>
@@ -43500,19 +43518,21 @@
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
       <c r="P384" t="inlineStr">
         <is>
-          <t>S Hemträskets sydspets, Srm</t>
+          <t>Hemträsket, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>698489</v>
+        <v>698490</v>
       </c>
       <c r="R384" t="n">
-        <v>6555828</v>
+        <v>6555875</v>
       </c>
       <c r="S384" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -43550,39 +43570,31 @@
       <c r="AE384" t="b">
         <v>0</v>
       </c>
+      <c r="AF384" t="inlineStr"/>
       <c r="AG384" t="b">
         <v>0</v>
-      </c>
-      <c r="AO384" t="inlineStr">
-        <is>
-          <t>Gammal tall (GAMTALL)</t>
-        </is>
       </c>
       <c r="AT384" t="inlineStr"/>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY384" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr"/>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498521</t>
+          <t>https://artportalen.se/Sighting/73702559</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>128410074</v>
+        <v>107498521</v>
       </c>
       <c r="B385" t="n">
         <v>92348</v>
@@ -43610,27 +43622,20 @@
           <t>(Fr.) Pat.</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
-      <c r="N385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
       <c r="P385" t="inlineStr">
         <is>
-          <t>Kärrgrav, Srm</t>
+          <t>S Hemträskets sydspets, Srm</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>698431</v>
+        <v>698489</v>
       </c>
       <c r="R385" t="n">
-        <v>6555927</v>
+        <v>6555828</v>
       </c>
       <c r="S385" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -43654,22 +43659,12 @@
       </c>
       <c r="Y385" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z385" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB385" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -43680,58 +43675,67 @@
       </c>
       <c r="AG385" t="b">
         <v>0</v>
+      </c>
+      <c r="AO385" t="inlineStr">
+        <is>
+          <t>Gammal tall (GAMTALL)</t>
+        </is>
       </c>
       <c r="AT385" t="inlineStr"/>
       <c r="AW385" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
-        </is>
-      </c>
-      <c r="AY385" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY385" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ385" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128410074</t>
+          <t>https://artportalen.se/Sighting/107498521</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>125602523</v>
+        <v>128410074</v>
       </c>
       <c r="B386" t="n">
-        <v>91930</v>
+        <v>92348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J386" t="inlineStr"/>
@@ -43743,13 +43747,13 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>698467</v>
+        <v>698431</v>
       </c>
       <c r="R386" t="n">
-        <v>6555935</v>
+        <v>6555927</v>
       </c>
       <c r="S386" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -43773,22 +43777,22 @@
       </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -43814,16 +43818,16 @@
       <c r="AY386" t="inlineStr"/>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125602523</t>
+          <t>https://artportalen.se/Sighting/128410074</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>73702534</v>
+        <v>125602523</v>
       </c>
       <c r="B387" t="n">
-        <v>93233</v>
+        <v>91930</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -43831,39 +43835,44 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>5964</v>
+        <v>5442</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
       <c r="P387" t="inlineStr">
         <is>
-          <t>Hemträsket, S om sydspetsen, Srm</t>
+          <t>Kärrgrav, Srm</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>698536</v>
+        <v>698467</v>
       </c>
       <c r="R387" t="n">
-        <v>6555855</v>
+        <v>6555935</v>
       </c>
       <c r="S387" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -43887,12 +43896,22 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -43901,31 +43920,30 @@
       <c r="AE387" t="b">
         <v>0</v>
       </c>
-      <c r="AF387" t="inlineStr"/>
       <c r="AG387" t="b">
         <v>0</v>
       </c>
       <c r="AT387" t="inlineStr"/>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702534</t>
+          <t>https://artportalen.se/Sighting/125602523</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>107498515</v>
+        <v>73702534</v>
       </c>
       <c r="B388" t="n">
         <v>93233</v>
@@ -43954,19 +43972,21 @@
         </is>
       </c>
       <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
       <c r="P388" t="inlineStr">
         <is>
-          <t>S Hemträskets sydspets, Srm</t>
+          <t>Hemträsket, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>698489</v>
+        <v>698536</v>
       </c>
       <c r="R388" t="n">
-        <v>6555828</v>
+        <v>6555855</v>
       </c>
       <c r="S388" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -44004,37 +44024,34 @@
       <c r="AE388" t="b">
         <v>0</v>
       </c>
+      <c r="AF388" t="inlineStr"/>
       <c r="AG388" t="b">
         <v>0</v>
       </c>
       <c r="AT388" t="inlineStr"/>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY388" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY388" t="inlineStr"/>
       <c r="AZ388" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498515</t>
+          <t>https://artportalen.se/Sighting/73702534</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>107498511</v>
+        <v>107498515</v>
       </c>
       <c r="B389" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -44042,21 +44059,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
@@ -44131,62 +44148,54 @@
       </c>
       <c r="AZ389" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498511</t>
+          <t>https://artportalen.se/Sighting/107498515</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>125602257</v>
+        <v>107498511</v>
       </c>
       <c r="B390" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I390" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K390" t="inlineStr"/>
-      <c r="L390" t="inlineStr"/>
-      <c r="M390" t="inlineStr"/>
-      <c r="N390" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
-          <t>Kärrgrav, Srm</t>
+          <t>S Hemträskets sydspets, Srm</t>
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>698452</v>
+        <v>698489</v>
       </c>
       <c r="R390" t="n">
-        <v>6555939</v>
+        <v>6555828</v>
       </c>
       <c r="S390" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -44210,22 +44219,12 @@
       </c>
       <c r="Y390" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z390" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB390" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -44240,27 +44239,31 @@
       <c r="AT390" t="inlineStr"/>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
-        </is>
-      </c>
-      <c r="AY390" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY390" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125602257</t>
+          <t>https://artportalen.se/Sighting/107498511</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>73702569</v>
+        <v>125602257</v>
       </c>
       <c r="B391" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -44268,46 +44271,45 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I391" t="inlineStr"/>
-      <c r="J391" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr"/>
       <c r="P391" t="inlineStr">
         <is>
-          <t>Hemträsket, S om sydspetsen, Srm</t>
+          <t>Kärrgrav, Srm</t>
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>698445</v>
+        <v>698452</v>
       </c>
       <c r="R391" t="n">
-        <v>6555856</v>
+        <v>6555939</v>
       </c>
       <c r="S391" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T391" t="inlineStr">
         <is>
@@ -44331,12 +44333,22 @@
       </c>
       <c r="Y391" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD391" t="b">
@@ -44345,31 +44357,30 @@
       <c r="AE391" t="b">
         <v>0</v>
       </c>
-      <c r="AF391" t="inlineStr"/>
       <c r="AG391" t="b">
         <v>0</v>
       </c>
       <c r="AT391" t="inlineStr"/>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
       <c r="AZ391" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702569</t>
+          <t>https://artportalen.se/Sighting/125602257</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>107498516</v>
+        <v>73702569</v>
       </c>
       <c r="B392" t="n">
         <v>5179</v>
@@ -44398,19 +44409,28 @@
         </is>
       </c>
       <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr"/>
       <c r="P392" t="inlineStr">
         <is>
-          <t>S Hemträskets sydspets, Srm</t>
+          <t>Hemträsket, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>698489</v>
+        <v>698445</v>
       </c>
       <c r="R392" t="n">
-        <v>6555828</v>
+        <v>6555856</v>
       </c>
       <c r="S392" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>
@@ -44448,84 +44468,72 @@
       <c r="AE392" t="b">
         <v>0</v>
       </c>
+      <c r="AF392" t="inlineStr"/>
       <c r="AG392" t="b">
         <v>0</v>
-      </c>
-      <c r="AO392" t="inlineStr">
-        <is>
-          <t>Torrträd (TORRTRÄD)</t>
-        </is>
       </c>
       <c r="AT392" t="inlineStr"/>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY392" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY392" t="inlineStr"/>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498516</t>
+          <t>https://artportalen.se/Sighting/73702569</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>73702554</v>
+        <v>107498516</v>
       </c>
       <c r="B393" t="n">
-        <v>111390</v>
+        <v>5179</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I393" t="inlineStr"/>
-      <c r="J393" t="inlineStr"/>
-      <c r="K393" t="inlineStr"/>
-      <c r="L393" t="inlineStr"/>
-      <c r="N393" t="inlineStr"/>
       <c r="P393" t="inlineStr">
         <is>
-          <t>Hemträsket, S om sydspetsen, Srm</t>
+          <t>S Hemträskets sydspets, Srm</t>
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>698519</v>
+        <v>698489</v>
       </c>
       <c r="R393" t="n">
-        <v>6555839</v>
+        <v>6555828</v>
       </c>
       <c r="S393" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="T393" t="inlineStr">
         <is>
@@ -44563,31 +44571,39 @@
       <c r="AE393" t="b">
         <v>0</v>
       </c>
-      <c r="AF393" t="inlineStr"/>
       <c r="AG393" t="b">
         <v>0</v>
+      </c>
+      <c r="AO393" t="inlineStr">
+        <is>
+          <t>Torrträd (TORRTRÄD)</t>
+        </is>
       </c>
       <c r="AT393" t="inlineStr"/>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY393" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY393" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ393" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702554</t>
+          <t>https://artportalen.se/Sighting/107498516</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>73702585</v>
+        <v>73702554</v>
       </c>
       <c r="B394" t="n">
         <v>111390</v>
@@ -44626,10 +44642,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>698460</v>
+        <v>698519</v>
       </c>
       <c r="R394" t="n">
-        <v>6555937</v>
+        <v>6555839</v>
       </c>
       <c r="S394" t="n">
         <v>5</v>
@@ -44688,13 +44704,13 @@
       <c r="AY394" t="inlineStr"/>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702585</t>
+          <t>https://artportalen.se/Sighting/73702554</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>107498517</v>
+        <v>73702585</v>
       </c>
       <c r="B395" t="n">
         <v>111390</v>
@@ -44723,19 +44739,23 @@
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
       <c r="P395" t="inlineStr">
         <is>
-          <t>S Hemträskets sydspets, Srm</t>
+          <t>Hemträsket, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>698489</v>
+        <v>698460</v>
       </c>
       <c r="R395" t="n">
-        <v>6555828</v>
+        <v>6555937</v>
       </c>
       <c r="S395" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -44773,79 +44793,72 @@
       <c r="AE395" t="b">
         <v>0</v>
       </c>
+      <c r="AF395" t="inlineStr"/>
       <c r="AG395" t="b">
         <v>0</v>
       </c>
       <c r="AT395" t="inlineStr"/>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY395" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY395" t="inlineStr"/>
       <c r="AZ395" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498517</t>
+          <t>https://artportalen.se/Sighting/73702585</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>125602258</v>
+        <v>107498517</v>
       </c>
       <c r="B396" t="n">
-        <v>99035</v>
+        <v>111390</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>219790</v>
+        <v>219711</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
-      <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
-      <c r="N396" t="inlineStr"/>
       <c r="P396" t="inlineStr">
         <is>
-          <t>Kärrgrav, Srm</t>
+          <t>S Hemträskets sydspets, Srm</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>698452</v>
+        <v>698489</v>
       </c>
       <c r="R396" t="n">
-        <v>6555939</v>
+        <v>6555828</v>
       </c>
       <c r="S396" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="T396" t="inlineStr">
         <is>
@@ -44869,22 +44882,12 @@
       </c>
       <c r="Y396" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z396" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB396" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD396" t="b">
@@ -44899,27 +44902,31 @@
       <c r="AT396" t="inlineStr"/>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
-        </is>
-      </c>
-      <c r="AY396" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY396" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ396" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125602258</t>
+          <t>https://artportalen.se/Sighting/107498517</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>128414906</v>
+        <v>125602258</v>
       </c>
       <c r="B397" t="n">
-        <v>106244</v>
+        <v>99035</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -44927,30 +44934,26 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr"/>
       <c r="N397" t="inlineStr"/>
       <c r="P397" t="inlineStr">
@@ -44959,13 +44962,13 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>698493</v>
+        <v>698452</v>
       </c>
       <c r="R397" t="n">
-        <v>6555906</v>
+        <v>6555939</v>
       </c>
       <c r="S397" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="T397" t="inlineStr">
         <is>
@@ -44989,22 +44992,22 @@
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z397" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -45030,16 +45033,16 @@
       <c r="AY397" t="inlineStr"/>
       <c r="AZ397" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128414906</t>
+          <t>https://artportalen.se/Sighting/125602258</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>125932368</v>
+        <v>128414906</v>
       </c>
       <c r="B398" t="n">
-        <v>99035</v>
+        <v>106244</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -45047,46 +45050,45 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr"/>
+      <c r="N398" t="inlineStr"/>
       <c r="P398" t="inlineStr">
         <is>
-          <t>Lusten, Lusten, Srm</t>
+          <t>Kärrgrav, Srm</t>
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>698879</v>
+        <v>698493</v>
       </c>
       <c r="R398" t="n">
-        <v>6553775</v>
+        <v>6555906</v>
       </c>
       <c r="S398" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="T398" t="inlineStr">
         <is>
@@ -45110,22 +45112,22 @@
       </c>
       <c r="Y398" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z398" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB398" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD398" t="b">
@@ -45140,55 +45142,59 @@
       <c r="AT398" t="inlineStr"/>
       <c r="AW398" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
       <c r="AZ398" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125932368</t>
+          <t>https://artportalen.se/Sighting/128414906</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>125931759</v>
+        <v>125932368</v>
       </c>
       <c r="B399" t="n">
-        <v>102560</v>
+        <v>99035</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>222133</v>
+        <v>219790</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I399" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P399" t="inlineStr">
@@ -45197,10 +45203,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>698870</v>
+        <v>698879</v>
       </c>
       <c r="R399" t="n">
-        <v>6553787</v>
+        <v>6553775</v>
       </c>
       <c r="S399" t="n">
         <v>1</v>
@@ -45232,7 +45238,7 @@
       </c>
       <c r="Z399" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA399" t="inlineStr">
@@ -45242,7 +45248,7 @@
       </c>
       <c r="AB399" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD399" t="b">
@@ -45268,16 +45274,16 @@
       <c r="AY399" t="inlineStr"/>
       <c r="AZ399" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125931759</t>
+          <t>https://artportalen.se/Sighting/125932368</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>134670281</v>
+        <v>125931759</v>
       </c>
       <c r="B400" t="n">
-        <v>102637</v>
+        <v>102560</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -45303,16 +45309,21 @@
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P400" t="inlineStr">
         <is>
-          <t>Lustehagen, Lustehagen, Srm</t>
+          <t>Lusten, Lusten, Srm</t>
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>698832</v>
+        <v>698870</v>
       </c>
       <c r="R400" t="n">
-        <v>6553794</v>
+        <v>6553787</v>
       </c>
       <c r="S400" t="n">
         <v>1</v>
@@ -45339,22 +45350,22 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="Z400" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD400" t="b">
@@ -45380,59 +45391,54 @@
       <c r="AY400" t="inlineStr"/>
       <c r="AZ400" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134670281</t>
+          <t>https://artportalen.se/Sighting/125931759</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>126314579</v>
+        <v>134670281</v>
       </c>
       <c r="B401" t="n">
-        <v>99038</v>
+        <v>102637</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>223597</v>
+        <v>222133</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
           <t>Lustehagen, Lustehagen, Srm</t>
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>698879</v>
+        <v>698832</v>
       </c>
       <c r="R401" t="n">
         <v>6553794</v>
       </c>
       <c r="S401" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -45456,22 +45462,22 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z401" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD401" t="b">
@@ -45497,16 +45503,16 @@
       <c r="AY401" t="inlineStr"/>
       <c r="AZ401" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126314579</t>
+          <t>https://artportalen.se/Sighting/134670281</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>134670368</v>
+        <v>126314579</v>
       </c>
       <c r="B402" t="n">
-        <v>99115</v>
+        <v>99038</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -45527,7 +45533,11 @@
         </is>
       </c>
       <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K402" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -45539,13 +45549,13 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>698832</v>
+        <v>698879</v>
       </c>
       <c r="R402" t="n">
         <v>6553794</v>
       </c>
       <c r="S402" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -45569,22 +45579,22 @@
       </c>
       <c r="Y402" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="Z402" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA402" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AB402" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD402" t="b">
@@ -45610,54 +45620,55 @@
       <c r="AY402" t="inlineStr"/>
       <c r="AZ402" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134670368</t>
+          <t>https://artportalen.se/Sighting/126314579</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>89165802</v>
+        <v>134670368</v>
       </c>
       <c r="B403" t="n">
-        <v>93197</v>
+        <v>99115</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>4364</v>
+        <v>223597</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P403" t="inlineStr">
         <is>
-          <t>Norra skogen, Srm</t>
+          <t>Lustehagen, Lustehagen, Srm</t>
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>698698</v>
+        <v>698832</v>
       </c>
       <c r="R403" t="n">
-        <v>6553972</v>
+        <v>6553794</v>
       </c>
       <c r="S403" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -45681,12 +45692,22 @@
       </c>
       <c r="Y403" t="inlineStr">
         <is>
-          <t>2020-09-13</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
-          <t>2020-09-13</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB403" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD403" t="b">
@@ -45701,31 +45722,27 @@
       <c r="AT403" t="inlineStr"/>
       <c r="AW403" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY403" t="inlineStr">
-        <is>
-          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
-        </is>
-      </c>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY403" t="inlineStr"/>
       <c r="AZ403" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165802</t>
+          <t>https://artportalen.se/Sighting/134670368</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>73849793</v>
+        <v>89165802</v>
       </c>
       <c r="B404" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -45733,39 +45750,37 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr"/>
       <c r="P404" t="inlineStr">
         <is>
-          <t>Fiversättra, SV om, Srm</t>
+          <t>Norra skogen, Srm</t>
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>698867</v>
+        <v>698698</v>
       </c>
       <c r="R404" t="n">
-        <v>6553974</v>
+        <v>6553972</v>
       </c>
       <c r="S404" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -45789,12 +45804,12 @@
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2020-09-13</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2020-09-13</t>
         </is>
       </c>
       <c r="AD404" t="b">
@@ -45803,31 +45818,34 @@
       <c r="AE404" t="b">
         <v>0</v>
       </c>
-      <c r="AF404" t="inlineStr"/>
       <c r="AG404" t="b">
         <v>0</v>
       </c>
       <c r="AT404" t="inlineStr"/>
       <c r="AW404" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY404" t="inlineStr"/>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY404" t="inlineStr">
+        <is>
+          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
       <c r="AZ404" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73849793</t>
+          <t>https://artportalen.se/Sighting/89165802</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>73850295</v>
+        <v>73849793</v>
       </c>
       <c r="B405" t="n">
         <v>91930</v>
@@ -45864,10 +45882,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>698762</v>
+        <v>698867</v>
       </c>
       <c r="R405" t="n">
-        <v>6554089</v>
+        <v>6553974</v>
       </c>
       <c r="S405" t="n">
         <v>5</v>
@@ -45926,13 +45944,13 @@
       <c r="AY405" t="inlineStr"/>
       <c r="AZ405" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850295</t>
+          <t>https://artportalen.se/Sighting/73849793</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>73850312</v>
+        <v>73850295</v>
       </c>
       <c r="B406" t="n">
         <v>91930</v>
@@ -45969,10 +45987,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>698704</v>
+        <v>698762</v>
       </c>
       <c r="R406" t="n">
-        <v>6554067</v>
+        <v>6554089</v>
       </c>
       <c r="S406" t="n">
         <v>5</v>
@@ -46031,16 +46049,16 @@
       <c r="AY406" t="inlineStr"/>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850312</t>
+          <t>https://artportalen.se/Sighting/73850295</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>73849756</v>
+        <v>73850312</v>
       </c>
       <c r="B407" t="n">
-        <v>93235</v>
+        <v>91930</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -46048,33 +46066,25 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J407" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr"/>
       <c r="P407" t="inlineStr">
         <is>
@@ -46082,10 +46092,10 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>698867</v>
+        <v>698704</v>
       </c>
       <c r="R407" t="n">
-        <v>6553974</v>
+        <v>6554067</v>
       </c>
       <c r="S407" t="n">
         <v>5</v>
@@ -46120,11 +46130,6 @@
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="AC407" t="inlineStr">
-        <is>
-          <t>Bergbunden mark med gammal tall.</t>
-        </is>
-      </c>
       <c r="AD407" t="b">
         <v>0</v>
       </c>
@@ -46149,16 +46154,16 @@
       <c r="AY407" t="inlineStr"/>
       <c r="AZ407" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73849756</t>
+          <t>https://artportalen.se/Sighting/73850312</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>73850169</v>
+        <v>73849756</v>
       </c>
       <c r="B408" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -46166,25 +46171,33 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I408" t="inlineStr"/>
-      <c r="J408" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K408" t="inlineStr"/>
       <c r="P408" t="inlineStr">
         <is>
@@ -46192,10 +46205,10 @@
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>698726</v>
+        <v>698867</v>
       </c>
       <c r="R408" t="n">
-        <v>6553919</v>
+        <v>6553974</v>
       </c>
       <c r="S408" t="n">
         <v>5</v>
@@ -46232,7 +46245,7 @@
       </c>
       <c r="AC408" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran i kanten mot sumpskog.</t>
+          <t>Bergbunden mark med gammal tall.</t>
         </is>
       </c>
       <c r="AD408" t="b">
@@ -46259,13 +46272,13 @@
       <c r="AY408" t="inlineStr"/>
       <c r="AZ408" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850169</t>
+          <t>https://artportalen.se/Sighting/73849756</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>73850191</v>
+        <v>73850169</v>
       </c>
       <c r="B409" t="n">
         <v>75428</v>
@@ -46302,10 +46315,10 @@
         </is>
       </c>
       <c r="Q409" t="n">
-        <v>698748</v>
+        <v>698726</v>
       </c>
       <c r="R409" t="n">
-        <v>6553932</v>
+        <v>6553919</v>
       </c>
       <c r="S409" t="n">
         <v>5</v>
@@ -46342,7 +46355,7 @@
       </c>
       <c r="AC409" t="inlineStr">
         <is>
-          <t>Rikligt på en gammal senvuxen gran i kanten mor sumpskog.</t>
+          <t>På gammal senvuxen gran i kanten mot sumpskog.</t>
         </is>
       </c>
       <c r="AD409" t="b">
@@ -46369,63 +46382,53 @@
       <c r="AY409" t="inlineStr"/>
       <c r="AZ409" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850191</t>
+          <t>https://artportalen.se/Sighting/73850169</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>73850223</v>
+        <v>73850191</v>
       </c>
       <c r="B410" t="n">
-        <v>57950</v>
+        <v>75428</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I410" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
-      <c r="L410" t="inlineStr"/>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N410" t="inlineStr"/>
       <c r="P410" t="inlineStr">
         <is>
           <t>Fiversättra, SV om, Srm</t>
         </is>
       </c>
       <c r="Q410" t="n">
-        <v>698795</v>
+        <v>698748</v>
       </c>
       <c r="R410" t="n">
-        <v>6553959</v>
+        <v>6553932</v>
       </c>
       <c r="S410" t="n">
         <v>5</v>
@@ -46462,7 +46465,7 @@
       </c>
       <c r="AC410" t="inlineStr">
         <is>
-          <t>Hackande och födosökande på död tall.</t>
+          <t>Rikligt på en gammal senvuxen gran i kanten mor sumpskog.</t>
         </is>
       </c>
       <c r="AD410" t="b">
@@ -46471,6 +46474,7 @@
       <c r="AE410" t="b">
         <v>0</v>
       </c>
+      <c r="AF410" t="inlineStr"/>
       <c r="AG410" t="b">
         <v>0</v>
       </c>
@@ -46488,16 +46492,16 @@
       <c r="AY410" t="inlineStr"/>
       <c r="AZ410" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850223</t>
+          <t>https://artportalen.se/Sighting/73850191</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>73850048</v>
+        <v>73850223</v>
       </c>
       <c r="B411" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -46505,30 +46509,33 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr"/>
       <c r="M411" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N411" t="inlineStr"/>
@@ -46538,10 +46545,10 @@
         </is>
       </c>
       <c r="Q411" t="n">
-        <v>698720</v>
+        <v>698795</v>
       </c>
       <c r="R411" t="n">
-        <v>6553901</v>
+        <v>6553959</v>
       </c>
       <c r="S411" t="n">
         <v>5</v>
@@ -46578,7 +46585,7 @@
       </c>
       <c r="AC411" t="inlineStr">
         <is>
-          <t>Gnagspår på torrgran.</t>
+          <t>Hackande och födosökande på död tall.</t>
         </is>
       </c>
       <c r="AD411" t="b">
@@ -46587,7 +46594,6 @@
       <c r="AE411" t="b">
         <v>0</v>
       </c>
-      <c r="AF411" t="inlineStr"/>
       <c r="AG411" t="b">
         <v>0</v>
       </c>
@@ -46605,16 +46611,16 @@
       <c r="AY411" t="inlineStr"/>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850048</t>
+          <t>https://artportalen.se/Sighting/73850223</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>73850379</v>
+        <v>73850048</v>
       </c>
       <c r="B412" t="n">
-        <v>44177</v>
+        <v>5179</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -46622,21 +46628,21 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I412" t="inlineStr"/>
@@ -46655,10 +46661,10 @@
         </is>
       </c>
       <c r="Q412" t="n">
-        <v>698693</v>
+        <v>698720</v>
       </c>
       <c r="R412" t="n">
-        <v>6553912</v>
+        <v>6553901</v>
       </c>
       <c r="S412" t="n">
         <v>5</v>
@@ -46695,7 +46701,7 @@
       </c>
       <c r="AC412" t="inlineStr">
         <is>
-          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+          <t>Gnagspår på torrgran.</t>
         </is>
       </c>
       <c r="AD412" t="b">
@@ -46722,16 +46728,16 @@
       <c r="AY412" t="inlineStr"/>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850379</t>
+          <t>https://artportalen.se/Sighting/73850048</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>73850425</v>
+        <v>73850379</v>
       </c>
       <c r="B413" t="n">
-        <v>5199</v>
+        <v>44177</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -46739,21 +46745,21 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I413" t="inlineStr"/>
@@ -46772,10 +46778,10 @@
         </is>
       </c>
       <c r="Q413" t="n">
-        <v>698707</v>
+        <v>698693</v>
       </c>
       <c r="R413" t="n">
-        <v>6553919</v>
+        <v>6553912</v>
       </c>
       <c r="S413" t="n">
         <v>5</v>
@@ -46812,7 +46818,7 @@
       </c>
       <c r="AC413" t="inlineStr">
         <is>
-          <t>Gnagspår på torrgran.</t>
+          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD413" t="b">
@@ -46839,16 +46845,16 @@
       <c r="AY413" t="inlineStr"/>
       <c r="AZ413" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850425</t>
+          <t>https://artportalen.se/Sighting/73850379</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>73849980</v>
+        <v>73850425</v>
       </c>
       <c r="B414" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -46856,21 +46862,21 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I414" t="inlineStr"/>
@@ -46879,7 +46885,7 @@
       <c r="L414" t="inlineStr"/>
       <c r="M414" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N414" t="inlineStr"/>
@@ -46889,10 +46895,10 @@
         </is>
       </c>
       <c r="Q414" t="n">
-        <v>698746</v>
+        <v>698707</v>
       </c>
       <c r="R414" t="n">
-        <v>6553900</v>
+        <v>6553919</v>
       </c>
       <c r="S414" t="n">
         <v>5</v>
@@ -46929,7 +46935,7 @@
       </c>
       <c r="AC414" t="inlineStr">
         <is>
-          <t>Gnagspår på nedfallen tallgren.</t>
+          <t>Gnagspår på torrgran.</t>
         </is>
       </c>
       <c r="AD414" t="b">
@@ -46956,53 +46962,60 @@
       <c r="AY414" t="inlineStr"/>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73849980</t>
+          <t>https://artportalen.se/Sighting/73850425</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>73850283</v>
+        <v>73849980</v>
       </c>
       <c r="B415" t="n">
-        <v>91930</v>
+        <v>8455</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr"/>
       <c r="P415" t="inlineStr">
         <is>
           <t>Fiversättra, SV om, Srm</t>
         </is>
       </c>
       <c r="Q415" t="n">
-        <v>698797</v>
+        <v>698746</v>
       </c>
       <c r="R415" t="n">
-        <v>6554091</v>
+        <v>6553900</v>
       </c>
       <c r="S415" t="n">
         <v>5</v>
@@ -47037,6 +47050,11 @@
           <t>2018-11-01</t>
         </is>
       </c>
+      <c r="AC415" t="inlineStr">
+        <is>
+          <t>Gnagspår på nedfallen tallgren.</t>
+        </is>
+      </c>
       <c r="AD415" t="b">
         <v>0</v>
       </c>
@@ -47061,54 +47079,56 @@
       <c r="AY415" t="inlineStr"/>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850283</t>
+          <t>https://artportalen.se/Sighting/73849980</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>89165788</v>
+        <v>73850283</v>
       </c>
       <c r="B416" t="n">
-        <v>92869</v>
+        <v>91930</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>4769</v>
+        <v>5442</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
       <c r="P416" t="inlineStr">
         <is>
-          <t>Norra skogen, Srm</t>
+          <t>Fiversättra, SV om, Srm</t>
         </is>
       </c>
       <c r="Q416" t="n">
-        <v>698820</v>
+        <v>698797</v>
       </c>
       <c r="R416" t="n">
-        <v>6554824</v>
+        <v>6554091</v>
       </c>
       <c r="S416" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -47132,12 +47152,12 @@
       </c>
       <c r="Y416" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="AA416" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="AD416" t="b">
@@ -47146,77 +47166,72 @@
       <c r="AE416" t="b">
         <v>0</v>
       </c>
+      <c r="AF416" t="inlineStr"/>
       <c r="AG416" t="b">
         <v>0</v>
       </c>
       <c r="AT416" t="inlineStr"/>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY416" t="inlineStr">
-        <is>
-          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY416" t="inlineStr"/>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165788</t>
+          <t>https://artportalen.se/Sighting/73850283</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>73702125</v>
+        <v>89165788</v>
       </c>
       <c r="B417" t="n">
-        <v>93197</v>
+        <v>92869</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I417" t="inlineStr"/>
-      <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr"/>
       <c r="P417" t="inlineStr">
         <is>
-          <t>Judeviken, SV om, Srm</t>
+          <t>Norra skogen, Srm</t>
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>698700</v>
+        <v>698820</v>
       </c>
       <c r="R417" t="n">
-        <v>6555057</v>
+        <v>6554824</v>
       </c>
       <c r="S417" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -47240,12 +47255,12 @@
       </c>
       <c r="Y417" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2020-10-02</t>
         </is>
       </c>
       <c r="AA417" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2020-10-02</t>
         </is>
       </c>
       <c r="AD417" t="b">
@@ -47254,81 +47269,74 @@
       <c r="AE417" t="b">
         <v>0</v>
       </c>
-      <c r="AF417" t="inlineStr"/>
       <c r="AG417" t="b">
         <v>0</v>
       </c>
       <c r="AT417" t="inlineStr"/>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY417" t="inlineStr"/>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY417" t="inlineStr">
+        <is>
+          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702125</t>
+          <t>https://artportalen.se/Sighting/89165788</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>73702111</v>
+        <v>73702125</v>
       </c>
       <c r="B418" t="n">
-        <v>57950</v>
+        <v>93197</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr"/>
-      <c r="L418" t="inlineStr"/>
-      <c r="M418" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N418" t="inlineStr"/>
       <c r="P418" t="inlineStr">
         <is>
           <t>Judeviken, SV om, Srm</t>
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>698679</v>
+        <v>698700</v>
       </c>
       <c r="R418" t="n">
-        <v>6555084</v>
+        <v>6555057</v>
       </c>
       <c r="S418" t="n">
         <v>5</v>
@@ -47369,6 +47377,7 @@
       <c r="AE418" t="b">
         <v>0</v>
       </c>
+      <c r="AF418" t="inlineStr"/>
       <c r="AG418" t="b">
         <v>0</v>
       </c>
@@ -47386,55 +47395,66 @@
       <c r="AY418" t="inlineStr"/>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702111</t>
+          <t>https://artportalen.se/Sighting/73702125</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>110700552</v>
+        <v>73702111</v>
       </c>
       <c r="B419" t="n">
-        <v>91930</v>
+        <v>57950</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr"/>
       <c r="P419" t="inlineStr">
         <is>
-          <t>Judeviken, Judeviken, Srm</t>
+          <t>Judeviken, SV om, Srm</t>
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>699050</v>
+        <v>698679</v>
       </c>
       <c r="R419" t="n">
-        <v>6555191</v>
+        <v>6555084</v>
       </c>
       <c r="S419" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -47458,22 +47478,12 @@
       </c>
       <c r="Y419" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z419" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA419" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB419" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD419" t="b">
@@ -47488,73 +47498,66 @@
       <c r="AT419" t="inlineStr"/>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110700552</t>
+          <t>https://artportalen.se/Sighting/73702111</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>73701908</v>
+        <v>110700552</v>
       </c>
       <c r="B420" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
-      <c r="L420" t="inlineStr"/>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N420" t="inlineStr"/>
       <c r="P420" t="inlineStr">
         <is>
-          <t>Judeviken, S om, Srm</t>
+          <t>Judeviken, Judeviken, Srm</t>
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>699152</v>
+        <v>699050</v>
       </c>
       <c r="R420" t="n">
-        <v>6555181</v>
+        <v>6555191</v>
       </c>
       <c r="S420" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -47578,12 +47581,22 @@
       </c>
       <c r="Y420" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AB420" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD420" t="b">
@@ -47598,64 +47611,70 @@
       <c r="AT420" t="inlineStr"/>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73701908</t>
+          <t>https://artportalen.se/Sighting/110700552</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>73701906</v>
+        <v>73701908</v>
       </c>
       <c r="B421" t="n">
-        <v>91930</v>
+        <v>57950</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I421" t="inlineStr"/>
-      <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr"/>
       <c r="P421" t="inlineStr">
         <is>
           <t>Judeviken, S om, Srm</t>
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>699183</v>
+        <v>699152</v>
       </c>
       <c r="R421" t="n">
-        <v>6555284</v>
+        <v>6555181</v>
       </c>
       <c r="S421" t="n">
         <v>5</v>
@@ -47696,7 +47715,6 @@
       <c r="AE421" t="b">
         <v>0</v>
       </c>
-      <c r="AF421" t="inlineStr"/>
       <c r="AG421" t="b">
         <v>0</v>
       </c>
@@ -47714,13 +47732,13 @@
       <c r="AY421" t="inlineStr"/>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73701906</t>
+          <t>https://artportalen.se/Sighting/73701908</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>107498525</v>
+        <v>73701906</v>
       </c>
       <c r="B422" t="n">
         <v>91930</v>
@@ -47749,19 +47767,21 @@
         </is>
       </c>
       <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
       <c r="P422" t="inlineStr">
         <is>
-          <t>Barrskog S om Judeviken, Srm</t>
+          <t>Judeviken, S om, Srm</t>
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>699054</v>
+        <v>699183</v>
       </c>
       <c r="R422" t="n">
-        <v>6555266</v>
+        <v>6555284</v>
       </c>
       <c r="S422" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -47799,64 +47819,56 @@
       <c r="AE422" t="b">
         <v>0</v>
       </c>
+      <c r="AF422" t="inlineStr"/>
       <c r="AG422" t="b">
         <v>0</v>
-      </c>
-      <c r="AO422" t="inlineStr">
-        <is>
-          <t>Gammal tall (GAMTALL)</t>
-        </is>
       </c>
       <c r="AT422" t="inlineStr"/>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY422" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY422" t="inlineStr"/>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498525</t>
+          <t>https://artportalen.se/Sighting/73701906</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>107498526</v>
+        <v>107498525</v>
       </c>
       <c r="B423" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I423" t="inlineStr"/>
@@ -47913,6 +47925,11 @@
       <c r="AG423" t="b">
         <v>0</v>
       </c>
+      <c r="AO423" t="inlineStr">
+        <is>
+          <t>Gammal tall (GAMTALL)</t>
+        </is>
+      </c>
       <c r="AT423" t="inlineStr"/>
       <c r="AW423" t="inlineStr">
         <is>
@@ -47931,16 +47948,16 @@
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498526</t>
+          <t>https://artportalen.se/Sighting/107498525</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>123423078</v>
+        <v>107498526</v>
       </c>
       <c r="B424" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -47948,37 +47965,37 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I424" t="inlineStr"/>
       <c r="P424" t="inlineStr">
         <is>
-          <t>Fiversättra, Fiversättra, Srm</t>
+          <t>Barrskog S om Judeviken, Srm</t>
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>699044</v>
+        <v>699054</v>
       </c>
       <c r="R424" t="n">
-        <v>6555239</v>
+        <v>6555266</v>
       </c>
       <c r="S424" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -48002,27 +48019,12 @@
       </c>
       <c r="Y424" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="Z424" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB424" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC424" t="inlineStr">
-        <is>
-          <t>Tjäderspillning på hälmark.</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD424" t="b">
@@ -48033,36 +48035,35 @@
       </c>
       <c r="AG424" t="b">
         <v>0</v>
-      </c>
-      <c r="AH424" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT424" t="inlineStr"/>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
-        </is>
-      </c>
-      <c r="AY424" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY424" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123423078</t>
+          <t>https://artportalen.se/Sighting/107498526</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>73701910</v>
+        <v>123423078</v>
       </c>
       <c r="B425" t="n">
-        <v>44177</v>
+        <v>57141</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -48070,46 +48071,37 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I425" t="inlineStr"/>
-      <c r="J425" t="inlineStr"/>
-      <c r="K425" t="inlineStr"/>
-      <c r="L425" t="inlineStr"/>
-      <c r="M425" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N425" t="inlineStr"/>
       <c r="P425" t="inlineStr">
         <is>
-          <t>Judeviken, S om, Srm</t>
+          <t>Fiversättra, Fiversättra, Srm</t>
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>699016</v>
+        <v>699044</v>
       </c>
       <c r="R425" t="n">
-        <v>6555314</v>
+        <v>6555239</v>
       </c>
       <c r="S425" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T425" t="inlineStr">
         <is>
@@ -48133,17 +48125,27 @@
       </c>
       <c r="Y425" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA425" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB425" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC425" t="inlineStr">
         <is>
-          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+          <t>Tjäderspillning på hälmark.</t>
         </is>
       </c>
       <c r="AD425" t="b">
@@ -48152,31 +48154,35 @@
       <c r="AE425" t="b">
         <v>0</v>
       </c>
-      <c r="AF425" t="inlineStr"/>
       <c r="AG425" t="b">
         <v>0</v>
+      </c>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT425" t="inlineStr"/>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73701910</t>
+          <t>https://artportalen.se/Sighting/123423078</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>107498523</v>
+        <v>73701910</v>
       </c>
       <c r="B426" t="n">
         <v>44177</v>
@@ -48205,19 +48211,28 @@
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr"/>
       <c r="P426" t="inlineStr">
         <is>
-          <t>Barrskog S om Judeviken, Srm</t>
+          <t>Judeviken, S om, Srm</t>
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>699054</v>
+        <v>699016</v>
       </c>
       <c r="R426" t="n">
-        <v>6555266</v>
+        <v>6555314</v>
       </c>
       <c r="S426" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -48249,37 +48264,145 @@
           <t>2018-10-23</t>
         </is>
       </c>
+      <c r="AC426" t="inlineStr">
+        <is>
+          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+        </is>
+      </c>
       <c r="AD426" t="b">
         <v>0</v>
       </c>
       <c r="AE426" t="b">
         <v>0</v>
       </c>
+      <c r="AF426" t="inlineStr"/>
       <c r="AG426" t="b">
         <v>0</v>
-      </c>
-      <c r="AO426" t="inlineStr">
-        <is>
-          <t>Låga av triviallövträd (LÖVLÅGA)</t>
-        </is>
       </c>
       <c r="AT426" t="inlineStr"/>
       <c r="AW426" t="inlineStr">
         <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX426" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73701910</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>107498523</v>
+      </c>
+      <c r="B427" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr"/>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>Barrskog S om Judeviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q427" t="n">
+        <v>699054</v>
+      </c>
+      <c r="R427" t="n">
+        <v>6555266</v>
+      </c>
+      <c r="S427" t="n">
+        <v>150</v>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AD427" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE427" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG427" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO427" t="inlineStr">
+        <is>
+          <t>Låga av triviallövträd (LÖVLÅGA)</t>
+        </is>
+      </c>
+      <c r="AT427" t="inlineStr"/>
+      <c r="AW427" t="inlineStr">
+        <is>
           <t>Anders Engström</t>
         </is>
       </c>
-      <c r="AX426" t="inlineStr">
+      <c r="AX427" t="inlineStr">
         <is>
           <t>Via Anders Engström</t>
         </is>
       </c>
-      <c r="AY426" t="inlineStr">
+      <c r="AY427" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
-      <c r="AZ426" t="inlineStr">
+      <c r="AZ427" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107498523</t>
         </is>
@@ -48712,6 +48835,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43466,6 +43466,7 @@
       <c r="AE383" t="b">
         <v>0</v>
       </c>
+      <c r="AF383" t="inlineStr"/>
       <c r="AG383" t="b">
         <v>0</v>
       </c>
@@ -43477,7 +43478,7 @@
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Emilia Blixt, Elis Bergman , Sanna Blixt</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ427"/>
+  <dimension ref="A1:AZ428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43944,10 +43944,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>73702534</v>
+        <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>93233</v>
+        <v>91607</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43955,39 +43955,44 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>5964</v>
+        <v>5733</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr"/>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Hemträsket, S om sydspetsen, Srm</t>
+          <t>Kärrgrav, Srm</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>698536</v>
+        <v>698523</v>
       </c>
       <c r="R388" t="n">
-        <v>6555855</v>
+        <v>6555862</v>
       </c>
       <c r="S388" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -44011,12 +44016,22 @@
       </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -44032,24 +44047,24 @@
       <c r="AT388" t="inlineStr"/>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt, Elis Bergman , Sanna Blixt</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
       <c r="AZ388" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702534</t>
+          <t>https://artportalen.se/Sighting/136730718</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>107498515</v>
+        <v>73702534</v>
       </c>
       <c r="B389" t="n">
         <v>93233</v>
@@ -44078,19 +44093,21 @@
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
-          <t>S Hemträskets sydspets, Srm</t>
+          <t>Hemträsket, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>698489</v>
+        <v>698536</v>
       </c>
       <c r="R389" t="n">
-        <v>6555828</v>
+        <v>6555855</v>
       </c>
       <c r="S389" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -44128,37 +44145,34 @@
       <c r="AE389" t="b">
         <v>0</v>
       </c>
+      <c r="AF389" t="inlineStr"/>
       <c r="AG389" t="b">
         <v>0</v>
       </c>
       <c r="AT389" t="inlineStr"/>
       <c r="AW389" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY389" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY389" t="inlineStr"/>
       <c r="AZ389" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498515</t>
+          <t>https://artportalen.se/Sighting/73702534</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>107498511</v>
+        <v>107498515</v>
       </c>
       <c r="B390" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -44166,21 +44180,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
@@ -44255,62 +44269,54 @@
       </c>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498511</t>
+          <t>https://artportalen.se/Sighting/107498515</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>125602257</v>
+        <v>107498511</v>
       </c>
       <c r="B391" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K391" t="inlineStr"/>
-      <c r="L391" t="inlineStr"/>
-      <c r="M391" t="inlineStr"/>
-      <c r="N391" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr"/>
       <c r="P391" t="inlineStr">
         <is>
-          <t>Kärrgrav, Srm</t>
+          <t>S Hemträskets sydspets, Srm</t>
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>698452</v>
+        <v>698489</v>
       </c>
       <c r="R391" t="n">
-        <v>6555939</v>
+        <v>6555828</v>
       </c>
       <c r="S391" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="T391" t="inlineStr">
         <is>
@@ -44334,22 +44340,12 @@
       </c>
       <c r="Y391" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z391" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB391" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD391" t="b">
@@ -44364,27 +44360,31 @@
       <c r="AT391" t="inlineStr"/>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
-        </is>
-      </c>
-      <c r="AY391" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY391" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ391" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125602257</t>
+          <t>https://artportalen.se/Sighting/107498511</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>73702569</v>
+        <v>125602257</v>
       </c>
       <c r="B392" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -44392,46 +44392,45 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I392" t="inlineStr"/>
-      <c r="J392" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr"/>
-      <c r="M392" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr"/>
       <c r="P392" t="inlineStr">
         <is>
-          <t>Hemträsket, S om sydspetsen, Srm</t>
+          <t>Kärrgrav, Srm</t>
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>698445</v>
+        <v>698452</v>
       </c>
       <c r="R392" t="n">
-        <v>6555856</v>
+        <v>6555939</v>
       </c>
       <c r="S392" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>
@@ -44455,12 +44454,22 @@
       </c>
       <c r="Y392" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD392" t="b">
@@ -44469,31 +44478,30 @@
       <c r="AE392" t="b">
         <v>0</v>
       </c>
-      <c r="AF392" t="inlineStr"/>
       <c r="AG392" t="b">
         <v>0</v>
       </c>
       <c r="AT392" t="inlineStr"/>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702569</t>
+          <t>https://artportalen.se/Sighting/125602257</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>107498516</v>
+        <v>73702569</v>
       </c>
       <c r="B393" t="n">
         <v>5179</v>
@@ -44522,19 +44530,28 @@
         </is>
       </c>
       <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr"/>
       <c r="P393" t="inlineStr">
         <is>
-          <t>S Hemträskets sydspets, Srm</t>
+          <t>Hemträsket, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>698489</v>
+        <v>698445</v>
       </c>
       <c r="R393" t="n">
-        <v>6555828</v>
+        <v>6555856</v>
       </c>
       <c r="S393" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T393" t="inlineStr">
         <is>
@@ -44572,84 +44589,72 @@
       <c r="AE393" t="b">
         <v>0</v>
       </c>
+      <c r="AF393" t="inlineStr"/>
       <c r="AG393" t="b">
         <v>0</v>
-      </c>
-      <c r="AO393" t="inlineStr">
-        <is>
-          <t>Torrträd (TORRTRÄD)</t>
-        </is>
       </c>
       <c r="AT393" t="inlineStr"/>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY393" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY393" t="inlineStr"/>
       <c r="AZ393" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498516</t>
+          <t>https://artportalen.se/Sighting/73702569</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>73702554</v>
+        <v>107498516</v>
       </c>
       <c r="B394" t="n">
-        <v>111390</v>
+        <v>5179</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I394" t="inlineStr"/>
-      <c r="J394" t="inlineStr"/>
-      <c r="K394" t="inlineStr"/>
-      <c r="L394" t="inlineStr"/>
-      <c r="N394" t="inlineStr"/>
       <c r="P394" t="inlineStr">
         <is>
-          <t>Hemträsket, S om sydspetsen, Srm</t>
+          <t>S Hemträskets sydspets, Srm</t>
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>698519</v>
+        <v>698489</v>
       </c>
       <c r="R394" t="n">
-        <v>6555839</v>
+        <v>6555828</v>
       </c>
       <c r="S394" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -44687,31 +44692,39 @@
       <c r="AE394" t="b">
         <v>0</v>
       </c>
-      <c r="AF394" t="inlineStr"/>
       <c r="AG394" t="b">
         <v>0</v>
+      </c>
+      <c r="AO394" t="inlineStr">
+        <is>
+          <t>Torrträd (TORRTRÄD)</t>
+        </is>
       </c>
       <c r="AT394" t="inlineStr"/>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY394" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY394" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702554</t>
+          <t>https://artportalen.se/Sighting/107498516</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>73702585</v>
+        <v>73702554</v>
       </c>
       <c r="B395" t="n">
         <v>111390</v>
@@ -44750,10 +44763,10 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>698460</v>
+        <v>698519</v>
       </c>
       <c r="R395" t="n">
-        <v>6555937</v>
+        <v>6555839</v>
       </c>
       <c r="S395" t="n">
         <v>5</v>
@@ -44812,13 +44825,13 @@
       <c r="AY395" t="inlineStr"/>
       <c r="AZ395" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702585</t>
+          <t>https://artportalen.se/Sighting/73702554</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>107498517</v>
+        <v>73702585</v>
       </c>
       <c r="B396" t="n">
         <v>111390</v>
@@ -44847,19 +44860,23 @@
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
       <c r="P396" t="inlineStr">
         <is>
-          <t>S Hemträskets sydspets, Srm</t>
+          <t>Hemträsket, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>698489</v>
+        <v>698460</v>
       </c>
       <c r="R396" t="n">
-        <v>6555828</v>
+        <v>6555937</v>
       </c>
       <c r="S396" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T396" t="inlineStr">
         <is>
@@ -44897,79 +44914,72 @@
       <c r="AE396" t="b">
         <v>0</v>
       </c>
+      <c r="AF396" t="inlineStr"/>
       <c r="AG396" t="b">
         <v>0</v>
       </c>
       <c r="AT396" t="inlineStr"/>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY396" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY396" t="inlineStr"/>
       <c r="AZ396" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498517</t>
+          <t>https://artportalen.se/Sighting/73702585</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>125602258</v>
+        <v>107498517</v>
       </c>
       <c r="B397" t="n">
-        <v>99035</v>
+        <v>111390</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>219790</v>
+        <v>219711</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
-      <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
-      <c r="N397" t="inlineStr"/>
       <c r="P397" t="inlineStr">
         <is>
-          <t>Kärrgrav, Srm</t>
+          <t>S Hemträskets sydspets, Srm</t>
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>698452</v>
+        <v>698489</v>
       </c>
       <c r="R397" t="n">
-        <v>6555939</v>
+        <v>6555828</v>
       </c>
       <c r="S397" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="T397" t="inlineStr">
         <is>
@@ -44993,22 +45003,12 @@
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z397" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB397" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -45023,27 +45023,31 @@
       <c r="AT397" t="inlineStr"/>
       <c r="AW397" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
-        </is>
-      </c>
-      <c r="AY397" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY397" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ397" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125602258</t>
+          <t>https://artportalen.se/Sighting/107498517</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>128414906</v>
+        <v>125602258</v>
       </c>
       <c r="B398" t="n">
-        <v>106244</v>
+        <v>99035</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -45051,30 +45055,26 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
       <c r="N398" t="inlineStr"/>
       <c r="P398" t="inlineStr">
@@ -45083,13 +45083,13 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>698493</v>
+        <v>698452</v>
       </c>
       <c r="R398" t="n">
-        <v>6555906</v>
+        <v>6555939</v>
       </c>
       <c r="S398" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="T398" t="inlineStr">
         <is>
@@ -45113,22 +45113,22 @@
       </c>
       <c r="Y398" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z398" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB398" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD398" t="b">
@@ -45154,16 +45154,16 @@
       <c r="AY398" t="inlineStr"/>
       <c r="AZ398" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128414906</t>
+          <t>https://artportalen.se/Sighting/125602258</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>125932368</v>
+        <v>128414906</v>
       </c>
       <c r="B399" t="n">
-        <v>99035</v>
+        <v>106244</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -45171,46 +45171,45 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I399" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
       <c r="P399" t="inlineStr">
         <is>
-          <t>Lusten, Lusten, Srm</t>
+          <t>Kärrgrav, Srm</t>
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>698879</v>
+        <v>698493</v>
       </c>
       <c r="R399" t="n">
-        <v>6553775</v>
+        <v>6555906</v>
       </c>
       <c r="S399" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="T399" t="inlineStr">
         <is>
@@ -45234,22 +45233,22 @@
       </c>
       <c r="Y399" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z399" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB399" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD399" t="b">
@@ -45264,55 +45263,59 @@
       <c r="AT399" t="inlineStr"/>
       <c r="AW399" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
       <c r="AZ399" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125932368</t>
+          <t>https://artportalen.se/Sighting/128414906</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>125931759</v>
+        <v>125932368</v>
       </c>
       <c r="B400" t="n">
-        <v>102560</v>
+        <v>99035</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>222133</v>
+        <v>219790</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I400" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P400" t="inlineStr">
@@ -45321,10 +45324,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>698870</v>
+        <v>698879</v>
       </c>
       <c r="R400" t="n">
-        <v>6553787</v>
+        <v>6553775</v>
       </c>
       <c r="S400" t="n">
         <v>1</v>
@@ -45356,7 +45359,7 @@
       </c>
       <c r="Z400" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
@@ -45366,7 +45369,7 @@
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD400" t="b">
@@ -45392,16 +45395,16 @@
       <c r="AY400" t="inlineStr"/>
       <c r="AZ400" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125931759</t>
+          <t>https://artportalen.se/Sighting/125932368</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>134670281</v>
+        <v>125931759</v>
       </c>
       <c r="B401" t="n">
-        <v>102637</v>
+        <v>102560</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -45427,16 +45430,21 @@
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P401" t="inlineStr">
         <is>
-          <t>Lustehagen, Lustehagen, Srm</t>
+          <t>Lusten, Lusten, Srm</t>
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>698832</v>
+        <v>698870</v>
       </c>
       <c r="R401" t="n">
-        <v>6553794</v>
+        <v>6553787</v>
       </c>
       <c r="S401" t="n">
         <v>1</v>
@@ -45463,22 +45471,22 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="Z401" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD401" t="b">
@@ -45504,59 +45512,54 @@
       <c r="AY401" t="inlineStr"/>
       <c r="AZ401" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134670281</t>
+          <t>https://artportalen.se/Sighting/125931759</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>126314579</v>
+        <v>134670281</v>
       </c>
       <c r="B402" t="n">
-        <v>99038</v>
+        <v>102637</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>223597</v>
+        <v>222133</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr"/>
       <c r="P402" t="inlineStr">
         <is>
           <t>Lustehagen, Lustehagen, Srm</t>
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>698879</v>
+        <v>698832</v>
       </c>
       <c r="R402" t="n">
         <v>6553794</v>
       </c>
       <c r="S402" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -45580,22 +45583,22 @@
       </c>
       <c r="Y402" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z402" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA402" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB402" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD402" t="b">
@@ -45621,16 +45624,16 @@
       <c r="AY402" t="inlineStr"/>
       <c r="AZ402" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126314579</t>
+          <t>https://artportalen.se/Sighting/134670281</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>134670368</v>
+        <v>126314579</v>
       </c>
       <c r="B403" t="n">
-        <v>99115</v>
+        <v>99038</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -45651,7 +45654,11 @@
         </is>
       </c>
       <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr"/>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K403" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -45663,13 +45670,13 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>698832</v>
+        <v>698879</v>
       </c>
       <c r="R403" t="n">
         <v>6553794</v>
       </c>
       <c r="S403" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -45693,22 +45700,22 @@
       </c>
       <c r="Y403" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="Z403" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AB403" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD403" t="b">
@@ -45734,54 +45741,55 @@
       <c r="AY403" t="inlineStr"/>
       <c r="AZ403" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134670368</t>
+          <t>https://artportalen.se/Sighting/126314579</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>89165802</v>
+        <v>134670368</v>
       </c>
       <c r="B404" t="n">
-        <v>93197</v>
+        <v>99115</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>4364</v>
+        <v>223597</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>Norra skogen, Srm</t>
+          <t>Lustehagen, Lustehagen, Srm</t>
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>698698</v>
+        <v>698832</v>
       </c>
       <c r="R404" t="n">
-        <v>6553972</v>
+        <v>6553794</v>
       </c>
       <c r="S404" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -45805,12 +45813,22 @@
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>2020-09-13</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
-          <t>2020-09-13</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB404" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD404" t="b">
@@ -45825,31 +45843,27 @@
       <c r="AT404" t="inlineStr"/>
       <c r="AW404" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY404" t="inlineStr">
-        <is>
-          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
-        </is>
-      </c>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY404" t="inlineStr"/>
       <c r="AZ404" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165802</t>
+          <t>https://artportalen.se/Sighting/134670368</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>73849793</v>
+        <v>89165802</v>
       </c>
       <c r="B405" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -45857,39 +45871,37 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I405" t="inlineStr"/>
-      <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr"/>
       <c r="P405" t="inlineStr">
         <is>
-          <t>Fiversättra, SV om, Srm</t>
+          <t>Norra skogen, Srm</t>
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>698867</v>
+        <v>698698</v>
       </c>
       <c r="R405" t="n">
-        <v>6553974</v>
+        <v>6553972</v>
       </c>
       <c r="S405" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -45913,12 +45925,12 @@
       </c>
       <c r="Y405" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2020-09-13</t>
         </is>
       </c>
       <c r="AA405" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2020-09-13</t>
         </is>
       </c>
       <c r="AD405" t="b">
@@ -45927,31 +45939,34 @@
       <c r="AE405" t="b">
         <v>0</v>
       </c>
-      <c r="AF405" t="inlineStr"/>
       <c r="AG405" t="b">
         <v>0</v>
       </c>
       <c r="AT405" t="inlineStr"/>
       <c r="AW405" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY405" t="inlineStr"/>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY405" t="inlineStr">
+        <is>
+          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
       <c r="AZ405" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73849793</t>
+          <t>https://artportalen.se/Sighting/89165802</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>73850295</v>
+        <v>73849793</v>
       </c>
       <c r="B406" t="n">
         <v>91930</v>
@@ -45988,10 +46003,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>698762</v>
+        <v>698867</v>
       </c>
       <c r="R406" t="n">
-        <v>6554089</v>
+        <v>6553974</v>
       </c>
       <c r="S406" t="n">
         <v>5</v>
@@ -46050,13 +46065,13 @@
       <c r="AY406" t="inlineStr"/>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850295</t>
+          <t>https://artportalen.se/Sighting/73849793</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>73850312</v>
+        <v>73850295</v>
       </c>
       <c r="B407" t="n">
         <v>91930</v>
@@ -46093,10 +46108,10 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>698704</v>
+        <v>698762</v>
       </c>
       <c r="R407" t="n">
-        <v>6554067</v>
+        <v>6554089</v>
       </c>
       <c r="S407" t="n">
         <v>5</v>
@@ -46155,16 +46170,16 @@
       <c r="AY407" t="inlineStr"/>
       <c r="AZ407" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850312</t>
+          <t>https://artportalen.se/Sighting/73850295</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>73849756</v>
+        <v>73850312</v>
       </c>
       <c r="B408" t="n">
-        <v>93235</v>
+        <v>91930</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -46172,33 +46187,25 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr"/>
       <c r="P408" t="inlineStr">
         <is>
@@ -46206,10 +46213,10 @@
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>698867</v>
+        <v>698704</v>
       </c>
       <c r="R408" t="n">
-        <v>6553974</v>
+        <v>6554067</v>
       </c>
       <c r="S408" t="n">
         <v>5</v>
@@ -46244,11 +46251,6 @@
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="AC408" t="inlineStr">
-        <is>
-          <t>Bergbunden mark med gammal tall.</t>
-        </is>
-      </c>
       <c r="AD408" t="b">
         <v>0</v>
       </c>
@@ -46273,16 +46275,16 @@
       <c r="AY408" t="inlineStr"/>
       <c r="AZ408" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73849756</t>
+          <t>https://artportalen.se/Sighting/73850312</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>73850169</v>
+        <v>73849756</v>
       </c>
       <c r="B409" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -46290,25 +46292,33 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I409" t="inlineStr"/>
-      <c r="J409" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K409" t="inlineStr"/>
       <c r="P409" t="inlineStr">
         <is>
@@ -46316,10 +46326,10 @@
         </is>
       </c>
       <c r="Q409" t="n">
-        <v>698726</v>
+        <v>698867</v>
       </c>
       <c r="R409" t="n">
-        <v>6553919</v>
+        <v>6553974</v>
       </c>
       <c r="S409" t="n">
         <v>5</v>
@@ -46356,7 +46366,7 @@
       </c>
       <c r="AC409" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran i kanten mot sumpskog.</t>
+          <t>Bergbunden mark med gammal tall.</t>
         </is>
       </c>
       <c r="AD409" t="b">
@@ -46383,13 +46393,13 @@
       <c r="AY409" t="inlineStr"/>
       <c r="AZ409" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850169</t>
+          <t>https://artportalen.se/Sighting/73849756</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>73850191</v>
+        <v>73850169</v>
       </c>
       <c r="B410" t="n">
         <v>75428</v>
@@ -46426,10 +46436,10 @@
         </is>
       </c>
       <c r="Q410" t="n">
-        <v>698748</v>
+        <v>698726</v>
       </c>
       <c r="R410" t="n">
-        <v>6553932</v>
+        <v>6553919</v>
       </c>
       <c r="S410" t="n">
         <v>5</v>
@@ -46466,7 +46476,7 @@
       </c>
       <c r="AC410" t="inlineStr">
         <is>
-          <t>Rikligt på en gammal senvuxen gran i kanten mor sumpskog.</t>
+          <t>På gammal senvuxen gran i kanten mot sumpskog.</t>
         </is>
       </c>
       <c r="AD410" t="b">
@@ -46493,63 +46503,53 @@
       <c r="AY410" t="inlineStr"/>
       <c r="AZ410" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850191</t>
+          <t>https://artportalen.se/Sighting/73850169</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>73850223</v>
+        <v>73850191</v>
       </c>
       <c r="B411" t="n">
-        <v>57950</v>
+        <v>75428</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
-      <c r="L411" t="inlineStr"/>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N411" t="inlineStr"/>
       <c r="P411" t="inlineStr">
         <is>
           <t>Fiversättra, SV om, Srm</t>
         </is>
       </c>
       <c r="Q411" t="n">
-        <v>698795</v>
+        <v>698748</v>
       </c>
       <c r="R411" t="n">
-        <v>6553959</v>
+        <v>6553932</v>
       </c>
       <c r="S411" t="n">
         <v>5</v>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="AC411" t="inlineStr">
         <is>
-          <t>Hackande och födosökande på död tall.</t>
+          <t>Rikligt på en gammal senvuxen gran i kanten mor sumpskog.</t>
         </is>
       </c>
       <c r="AD411" t="b">
@@ -46595,6 +46595,7 @@
       <c r="AE411" t="b">
         <v>0</v>
       </c>
+      <c r="AF411" t="inlineStr"/>
       <c r="AG411" t="b">
         <v>0</v>
       </c>
@@ -46612,16 +46613,16 @@
       <c r="AY411" t="inlineStr"/>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850223</t>
+          <t>https://artportalen.se/Sighting/73850191</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>73850048</v>
+        <v>73850223</v>
       </c>
       <c r="B412" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -46629,30 +46630,33 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I412" t="inlineStr"/>
-      <c r="J412" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr"/>
       <c r="M412" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N412" t="inlineStr"/>
@@ -46662,10 +46666,10 @@
         </is>
       </c>
       <c r="Q412" t="n">
-        <v>698720</v>
+        <v>698795</v>
       </c>
       <c r="R412" t="n">
-        <v>6553901</v>
+        <v>6553959</v>
       </c>
       <c r="S412" t="n">
         <v>5</v>
@@ -46702,7 +46706,7 @@
       </c>
       <c r="AC412" t="inlineStr">
         <is>
-          <t>Gnagspår på torrgran.</t>
+          <t>Hackande och födosökande på död tall.</t>
         </is>
       </c>
       <c r="AD412" t="b">
@@ -46711,7 +46715,6 @@
       <c r="AE412" t="b">
         <v>0</v>
       </c>
-      <c r="AF412" t="inlineStr"/>
       <c r="AG412" t="b">
         <v>0</v>
       </c>
@@ -46729,16 +46732,16 @@
       <c r="AY412" t="inlineStr"/>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850048</t>
+          <t>https://artportalen.se/Sighting/73850223</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>73850379</v>
+        <v>73850048</v>
       </c>
       <c r="B413" t="n">
-        <v>44177</v>
+        <v>5179</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -46746,21 +46749,21 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I413" t="inlineStr"/>
@@ -46779,10 +46782,10 @@
         </is>
       </c>
       <c r="Q413" t="n">
-        <v>698693</v>
+        <v>698720</v>
       </c>
       <c r="R413" t="n">
-        <v>6553912</v>
+        <v>6553901</v>
       </c>
       <c r="S413" t="n">
         <v>5</v>
@@ -46819,7 +46822,7 @@
       </c>
       <c r="AC413" t="inlineStr">
         <is>
-          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+          <t>Gnagspår på torrgran.</t>
         </is>
       </c>
       <c r="AD413" t="b">
@@ -46846,16 +46849,16 @@
       <c r="AY413" t="inlineStr"/>
       <c r="AZ413" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850379</t>
+          <t>https://artportalen.se/Sighting/73850048</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>73850425</v>
+        <v>73850379</v>
       </c>
       <c r="B414" t="n">
-        <v>5199</v>
+        <v>44177</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -46863,21 +46866,21 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I414" t="inlineStr"/>
@@ -46896,10 +46899,10 @@
         </is>
       </c>
       <c r="Q414" t="n">
-        <v>698707</v>
+        <v>698693</v>
       </c>
       <c r="R414" t="n">
-        <v>6553919</v>
+        <v>6553912</v>
       </c>
       <c r="S414" t="n">
         <v>5</v>
@@ -46936,7 +46939,7 @@
       </c>
       <c r="AC414" t="inlineStr">
         <is>
-          <t>Gnagspår på torrgran.</t>
+          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD414" t="b">
@@ -46963,16 +46966,16 @@
       <c r="AY414" t="inlineStr"/>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850425</t>
+          <t>https://artportalen.se/Sighting/73850379</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>73849980</v>
+        <v>73850425</v>
       </c>
       <c r="B415" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -46980,21 +46983,21 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I415" t="inlineStr"/>
@@ -47003,7 +47006,7 @@
       <c r="L415" t="inlineStr"/>
       <c r="M415" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N415" t="inlineStr"/>
@@ -47013,10 +47016,10 @@
         </is>
       </c>
       <c r="Q415" t="n">
-        <v>698746</v>
+        <v>698707</v>
       </c>
       <c r="R415" t="n">
-        <v>6553900</v>
+        <v>6553919</v>
       </c>
       <c r="S415" t="n">
         <v>5</v>
@@ -47053,7 +47056,7 @@
       </c>
       <c r="AC415" t="inlineStr">
         <is>
-          <t>Gnagspår på nedfallen tallgren.</t>
+          <t>Gnagspår på torrgran.</t>
         </is>
       </c>
       <c r="AD415" t="b">
@@ -47080,53 +47083,60 @@
       <c r="AY415" t="inlineStr"/>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73849980</t>
+          <t>https://artportalen.se/Sighting/73850425</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>73850283</v>
+        <v>73849980</v>
       </c>
       <c r="B416" t="n">
-        <v>91930</v>
+        <v>8455</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr"/>
       <c r="P416" t="inlineStr">
         <is>
           <t>Fiversättra, SV om, Srm</t>
         </is>
       </c>
       <c r="Q416" t="n">
-        <v>698797</v>
+        <v>698746</v>
       </c>
       <c r="R416" t="n">
-        <v>6554091</v>
+        <v>6553900</v>
       </c>
       <c r="S416" t="n">
         <v>5</v>
@@ -47161,6 +47171,11 @@
           <t>2018-11-01</t>
         </is>
       </c>
+      <c r="AC416" t="inlineStr">
+        <is>
+          <t>Gnagspår på nedfallen tallgren.</t>
+        </is>
+      </c>
       <c r="AD416" t="b">
         <v>0</v>
       </c>
@@ -47185,54 +47200,56 @@
       <c r="AY416" t="inlineStr"/>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73850283</t>
+          <t>https://artportalen.se/Sighting/73849980</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>89165788</v>
+        <v>73850283</v>
       </c>
       <c r="B417" t="n">
-        <v>92869</v>
+        <v>91930</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>4769</v>
+        <v>5442</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
       <c r="P417" t="inlineStr">
         <is>
-          <t>Norra skogen, Srm</t>
+          <t>Fiversättra, SV om, Srm</t>
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>698820</v>
+        <v>698797</v>
       </c>
       <c r="R417" t="n">
-        <v>6554824</v>
+        <v>6554091</v>
       </c>
       <c r="S417" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -47256,12 +47273,12 @@
       </c>
       <c r="Y417" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="AA417" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="AD417" t="b">
@@ -47270,77 +47287,72 @@
       <c r="AE417" t="b">
         <v>0</v>
       </c>
+      <c r="AF417" t="inlineStr"/>
       <c r="AG417" t="b">
         <v>0</v>
       </c>
       <c r="AT417" t="inlineStr"/>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY417" t="inlineStr">
-        <is>
-          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY417" t="inlineStr"/>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165788</t>
+          <t>https://artportalen.se/Sighting/73850283</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>73702125</v>
+        <v>89165788</v>
       </c>
       <c r="B418" t="n">
-        <v>93197</v>
+        <v>92869</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I418" t="inlineStr"/>
-      <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
       <c r="P418" t="inlineStr">
         <is>
-          <t>Judeviken, SV om, Srm</t>
+          <t>Norra skogen, Srm</t>
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>698700</v>
+        <v>698820</v>
       </c>
       <c r="R418" t="n">
-        <v>6555057</v>
+        <v>6554824</v>
       </c>
       <c r="S418" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -47364,12 +47376,12 @@
       </c>
       <c r="Y418" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2020-10-02</t>
         </is>
       </c>
       <c r="AA418" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2020-10-02</t>
         </is>
       </c>
       <c r="AD418" t="b">
@@ -47378,81 +47390,74 @@
       <c r="AE418" t="b">
         <v>0</v>
       </c>
-      <c r="AF418" t="inlineStr"/>
       <c r="AG418" t="b">
         <v>0</v>
       </c>
       <c r="AT418" t="inlineStr"/>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY418" t="inlineStr"/>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY418" t="inlineStr">
+        <is>
+          <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702125</t>
+          <t>https://artportalen.se/Sighting/89165788</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>73702111</v>
+        <v>73702125</v>
       </c>
       <c r="B419" t="n">
-        <v>57950</v>
+        <v>93197</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
-      <c r="L419" t="inlineStr"/>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N419" t="inlineStr"/>
       <c r="P419" t="inlineStr">
         <is>
           <t>Judeviken, SV om, Srm</t>
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>698679</v>
+        <v>698700</v>
       </c>
       <c r="R419" t="n">
-        <v>6555084</v>
+        <v>6555057</v>
       </c>
       <c r="S419" t="n">
         <v>5</v>
@@ -47493,6 +47498,7 @@
       <c r="AE419" t="b">
         <v>0</v>
       </c>
+      <c r="AF419" t="inlineStr"/>
       <c r="AG419" t="b">
         <v>0</v>
       </c>
@@ -47510,55 +47516,66 @@
       <c r="AY419" t="inlineStr"/>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73702111</t>
+          <t>https://artportalen.se/Sighting/73702125</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>110700552</v>
+        <v>73702111</v>
       </c>
       <c r="B420" t="n">
-        <v>91930</v>
+        <v>57950</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr"/>
       <c r="P420" t="inlineStr">
         <is>
-          <t>Judeviken, Judeviken, Srm</t>
+          <t>Judeviken, SV om, Srm</t>
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>699050</v>
+        <v>698679</v>
       </c>
       <c r="R420" t="n">
-        <v>6555191</v>
+        <v>6555084</v>
       </c>
       <c r="S420" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -47582,22 +47599,12 @@
       </c>
       <c r="Y420" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z420" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB420" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD420" t="b">
@@ -47612,73 +47619,66 @@
       <c r="AT420" t="inlineStr"/>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110700552</t>
+          <t>https://artportalen.se/Sighting/73702111</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>73701908</v>
+        <v>110700552</v>
       </c>
       <c r="B421" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
-      <c r="L421" t="inlineStr"/>
-      <c r="M421" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N421" t="inlineStr"/>
       <c r="P421" t="inlineStr">
         <is>
-          <t>Judeviken, S om, Srm</t>
+          <t>Judeviken, Judeviken, Srm</t>
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>699152</v>
+        <v>699050</v>
       </c>
       <c r="R421" t="n">
-        <v>6555181</v>
+        <v>6555191</v>
       </c>
       <c r="S421" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T421" t="inlineStr">
         <is>
@@ -47702,12 +47702,22 @@
       </c>
       <c r="Y421" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA421" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AB421" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD421" t="b">
@@ -47722,64 +47732,70 @@
       <c r="AT421" t="inlineStr"/>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73701908</t>
+          <t>https://artportalen.se/Sighting/110700552</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>73701906</v>
+        <v>73701908</v>
       </c>
       <c r="B422" t="n">
-        <v>91930</v>
+        <v>57950</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I422" t="inlineStr"/>
-      <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr"/>
       <c r="P422" t="inlineStr">
         <is>
           <t>Judeviken, S om, Srm</t>
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>699183</v>
+        <v>699152</v>
       </c>
       <c r="R422" t="n">
-        <v>6555284</v>
+        <v>6555181</v>
       </c>
       <c r="S422" t="n">
         <v>5</v>
@@ -47820,7 +47836,6 @@
       <c r="AE422" t="b">
         <v>0</v>
       </c>
-      <c r="AF422" t="inlineStr"/>
       <c r="AG422" t="b">
         <v>0</v>
       </c>
@@ -47838,13 +47853,13 @@
       <c r="AY422" t="inlineStr"/>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73701906</t>
+          <t>https://artportalen.se/Sighting/73701908</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>107498525</v>
+        <v>73701906</v>
       </c>
       <c r="B423" t="n">
         <v>91930</v>
@@ -47873,19 +47888,21 @@
         </is>
       </c>
       <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
       <c r="P423" t="inlineStr">
         <is>
-          <t>Barrskog S om Judeviken, Srm</t>
+          <t>Judeviken, S om, Srm</t>
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>699054</v>
+        <v>699183</v>
       </c>
       <c r="R423" t="n">
-        <v>6555266</v>
+        <v>6555284</v>
       </c>
       <c r="S423" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="T423" t="inlineStr">
         <is>
@@ -47923,64 +47940,56 @@
       <c r="AE423" t="b">
         <v>0</v>
       </c>
+      <c r="AF423" t="inlineStr"/>
       <c r="AG423" t="b">
         <v>0</v>
-      </c>
-      <c r="AO423" t="inlineStr">
-        <is>
-          <t>Gammal tall (GAMTALL)</t>
-        </is>
       </c>
       <c r="AT423" t="inlineStr"/>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY423" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY423" t="inlineStr"/>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498525</t>
+          <t>https://artportalen.se/Sighting/73701906</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>107498526</v>
+        <v>107498525</v>
       </c>
       <c r="B424" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I424" t="inlineStr"/>
@@ -48037,6 +48046,11 @@
       <c r="AG424" t="b">
         <v>0</v>
       </c>
+      <c r="AO424" t="inlineStr">
+        <is>
+          <t>Gammal tall (GAMTALL)</t>
+        </is>
+      </c>
       <c r="AT424" t="inlineStr"/>
       <c r="AW424" t="inlineStr">
         <is>
@@ -48055,16 +48069,16 @@
       </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107498526</t>
+          <t>https://artportalen.se/Sighting/107498525</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>123423078</v>
+        <v>107498526</v>
       </c>
       <c r="B425" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -48072,37 +48086,37 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I425" t="inlineStr"/>
       <c r="P425" t="inlineStr">
         <is>
-          <t>Fiversättra, Fiversättra, Srm</t>
+          <t>Barrskog S om Judeviken, Srm</t>
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>699044</v>
+        <v>699054</v>
       </c>
       <c r="R425" t="n">
-        <v>6555239</v>
+        <v>6555266</v>
       </c>
       <c r="S425" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="T425" t="inlineStr">
         <is>
@@ -48126,27 +48140,12 @@
       </c>
       <c r="Y425" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="Z425" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AA425" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB425" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC425" t="inlineStr">
-        <is>
-          <t>Tjäderspillning på hälmark.</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="AD425" t="b">
@@ -48157,36 +48156,35 @@
       </c>
       <c r="AG425" t="b">
         <v>0</v>
-      </c>
-      <c r="AH425" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT425" t="inlineStr"/>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
-        </is>
-      </c>
-      <c r="AY425" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY425" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123423078</t>
+          <t>https://artportalen.se/Sighting/107498526</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>73701910</v>
+        <v>123423078</v>
       </c>
       <c r="B426" t="n">
-        <v>44177</v>
+        <v>57141</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -48194,46 +48192,37 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
-      <c r="J426" t="inlineStr"/>
-      <c r="K426" t="inlineStr"/>
-      <c r="L426" t="inlineStr"/>
-      <c r="M426" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N426" t="inlineStr"/>
       <c r="P426" t="inlineStr">
         <is>
-          <t>Judeviken, S om, Srm</t>
+          <t>Fiversättra, Fiversättra, Srm</t>
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>699016</v>
+        <v>699044</v>
       </c>
       <c r="R426" t="n">
-        <v>6555314</v>
+        <v>6555239</v>
       </c>
       <c r="S426" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -48257,17 +48246,27 @@
       </c>
       <c r="Y426" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA426" t="inlineStr">
         <is>
-          <t>2018-10-23</t>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB426" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC426" t="inlineStr">
         <is>
-          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+          <t>Tjäderspillning på hälmark.</t>
         </is>
       </c>
       <c r="AD426" t="b">
@@ -48276,31 +48275,35 @@
       <c r="AE426" t="b">
         <v>0</v>
       </c>
-      <c r="AF426" t="inlineStr"/>
       <c r="AG426" t="b">
         <v>0</v>
+      </c>
+      <c r="AH426" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT426" t="inlineStr"/>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73701910</t>
+          <t>https://artportalen.se/Sighting/123423078</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>107498523</v>
+        <v>73701910</v>
       </c>
       <c r="B427" t="n">
         <v>44177</v>
@@ -48329,19 +48332,28 @@
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr"/>
       <c r="P427" t="inlineStr">
         <is>
-          <t>Barrskog S om Judeviken, Srm</t>
+          <t>Judeviken, S om, Srm</t>
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>699054</v>
+        <v>699016</v>
       </c>
       <c r="R427" t="n">
-        <v>6555266</v>
+        <v>6555314</v>
       </c>
       <c r="S427" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="T427" t="inlineStr">
         <is>
@@ -48373,37 +48385,145 @@
           <t>2018-10-23</t>
         </is>
       </c>
+      <c r="AC427" t="inlineStr">
+        <is>
+          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+        </is>
+      </c>
       <c r="AD427" t="b">
         <v>0</v>
       </c>
       <c r="AE427" t="b">
         <v>0</v>
       </c>
+      <c r="AF427" t="inlineStr"/>
       <c r="AG427" t="b">
         <v>0</v>
-      </c>
-      <c r="AO427" t="inlineStr">
-        <is>
-          <t>Låga av triviallövträd (LÖVLÅGA)</t>
-        </is>
       </c>
       <c r="AT427" t="inlineStr"/>
       <c r="AW427" t="inlineStr">
         <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX427" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73701910</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>107498523</v>
+      </c>
+      <c r="B428" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr"/>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>Barrskog S om Judeviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q428" t="n">
+        <v>699054</v>
+      </c>
+      <c r="R428" t="n">
+        <v>6555266</v>
+      </c>
+      <c r="S428" t="n">
+        <v>150</v>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W428" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="AD428" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE428" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG428" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO428" t="inlineStr">
+        <is>
+          <t>Låga av triviallövträd (LÖVLÅGA)</t>
+        </is>
+      </c>
+      <c r="AT428" t="inlineStr"/>
+      <c r="AW428" t="inlineStr">
+        <is>
           <t>Anders Engström</t>
         </is>
       </c>
-      <c r="AX427" t="inlineStr">
+      <c r="AX428" t="inlineStr">
         <is>
           <t>Via Anders Engström</t>
         </is>
       </c>
-      <c r="AY427" t="inlineStr">
+      <c r="AY428" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
-      <c r="AZ427" t="inlineStr">
+      <c r="AZ428" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107498523</t>
         </is>
@@ -48837,6 +48957,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91607</v>
+        <v>91609</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -44052,7 +44052,7 @@
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>Emilia Blixt, Elis Bergman , Sanna Blixt</t>
+          <t>Emilia Blixt, Sanna Blixt, Elis Bergman</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -44052,7 +44052,7 @@
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>Emilia Blixt, Sanna Blixt, Elis Bergman</t>
+          <t>Emilia Blixt, Elis Bergman , Sanna Blixt</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91613</v>
+        <v>91614</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91614</v>
+        <v>91620</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91620</v>
+        <v>91624</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91626</v>
+        <v>91639</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91641</v>
+        <v>91644</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91644</v>
+        <v>91654</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91654</v>
+        <v>91655</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91655</v>
+        <v>91658</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43369,7 +43369,7 @@
         <v>136730156</v>
       </c>
       <c r="B383" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -43947,7 +43947,7 @@
         <v>136730718</v>
       </c>
       <c r="B388" t="n">
-        <v>91660</v>
+        <v>91665</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
